--- a/data/obx_xlsx/KCCK.OL.xlsx
+++ b/data/obx_xlsx/KCCK.OL.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="337">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -5483,9 +5483,7 @@
       <c r="I11" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="J11" s="7" t="s">
-        <v>26</v>
-      </c>
+      <c r="J11" s="7"/>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
       <c r="A12" s="8" t="s">
@@ -5515,9 +5513,7 @@
       <c r="I12" s="9">
         <v>43465.0</v>
       </c>
-      <c r="J12" s="9">
-        <v>43100.0</v>
-      </c>
+      <c r="J12" s="9"/>
     </row>
     <row r="13" ht="15.0" customHeight="1" outlineLevel="1">
       <c r="A13" s="8" t="s">
@@ -5547,9 +5543,7 @@
       <c r="I13" s="9">
         <v>43830.0</v>
       </c>
-      <c r="J13" s="9">
-        <v>43465.0</v>
-      </c>
+      <c r="J13" s="9"/>
     </row>
     <row r="14" ht="15.0" customHeight="1" outlineLevel="1">
       <c r="A14" s="8" t="s">
@@ -5579,9 +5573,7 @@
       <c r="I14" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="J14" s="10" t="s">
-        <v>30</v>
-      </c>
+      <c r="J14" s="10"/>
     </row>
     <row r="15" ht="15.0" customHeight="1" outlineLevel="1">
       <c r="A15" s="8" t="s">
@@ -5611,9 +5603,7 @@
       <c r="I15" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="J15" s="10" t="s">
-        <v>142</v>
-      </c>
+      <c r="J15" s="10"/>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
       <c r="A16" s="8" t="s">
@@ -5671,9 +5661,7 @@
       <c r="I19" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="J19" s="13" t="s">
-        <v>44</v>
-      </c>
+      <c r="J19" s="13"/>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
@@ -5801,9 +5789,7 @@
         <v>-0.01</v>
       </c>
       <c r="I24" s="16"/>
-      <c r="J24" s="21">
-        <v>-0.02</v>
-      </c>
+      <c r="J24" s="21"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
@@ -7273,9 +7259,7 @@
       <c r="I80" s="16">
         <v>0.0</v>
       </c>
-      <c r="J80" s="16">
-        <v>0.0</v>
-      </c>
+      <c r="J80" s="16"/>
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
@@ -7305,9 +7289,7 @@
       <c r="I81" s="17">
         <v>40.57</v>
       </c>
-      <c r="J81" s="17">
-        <v>32.32</v>
-      </c>
+      <c r="J81" s="17"/>
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
@@ -7337,9 +7319,7 @@
       <c r="I82" s="17">
         <v>40.57</v>
       </c>
-      <c r="J82" s="17">
-        <v>32.32</v>
-      </c>
+      <c r="J82" s="17"/>
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
@@ -7623,9 +7603,7 @@
       <c r="I94" s="17">
         <v>40.57</v>
       </c>
-      <c r="J94" s="17">
-        <v>32.32</v>
-      </c>
+      <c r="J94" s="17"/>
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="14" t="s">
@@ -7655,9 +7633,7 @@
       <c r="I95" s="17">
         <v>1.0</v>
       </c>
-      <c r="J95" s="17">
-        <v>1.0</v>
-      </c>
+      <c r="J95" s="17"/>
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
@@ -7687,9 +7663,7 @@
       <c r="I96" s="16">
         <v>0.0</v>
       </c>
-      <c r="J96" s="16">
-        <v>0.0</v>
-      </c>
+      <c r="J96" s="16"/>
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
@@ -7719,9 +7693,7 @@
       <c r="I97" s="17">
         <v>40.57</v>
       </c>
-      <c r="J97" s="17">
-        <v>32.32</v>
-      </c>
+      <c r="J97" s="17"/>
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="14" t="s">
